--- a/artfynd/A 35790-2024 artfynd.xlsx
+++ b/artfynd/A 35790-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880276</v>
+        <v>119880274</v>
       </c>
       <c r="B3" t="n">
-        <v>78171</v>
+        <v>87406</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>4412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668982</v>
+        <v>668987</v>
       </c>
       <c r="R3" t="n">
-        <v>7181867</v>
+        <v>7181886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880274</v>
+        <v>119880279</v>
       </c>
       <c r="B4" t="n">
-        <v>87406</v>
+        <v>57463</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4412</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668987</v>
+        <v>669087</v>
       </c>
       <c r="R4" t="n">
-        <v>7181886</v>
+        <v>7181763</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880279</v>
+        <v>119880276</v>
       </c>
       <c r="B5" t="n">
-        <v>57463</v>
+        <v>78171</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669087</v>
+        <v>668982</v>
       </c>
       <c r="R5" t="n">
-        <v>7181763</v>
+        <v>7181867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35790-2024 artfynd.xlsx
+++ b/artfynd/A 35790-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880279</v>
+        <v>119880276</v>
       </c>
       <c r="B4" t="n">
-        <v>57463</v>
+        <v>78171</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>669087</v>
+        <v>668982</v>
       </c>
       <c r="R4" t="n">
-        <v>7181763</v>
+        <v>7181867</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880276</v>
+        <v>119880279</v>
       </c>
       <c r="B5" t="n">
-        <v>78171</v>
+        <v>57463</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668982</v>
+        <v>669087</v>
       </c>
       <c r="R5" t="n">
-        <v>7181867</v>
+        <v>7181763</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35790-2024 artfynd.xlsx
+++ b/artfynd/A 35790-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119880273</v>
+        <v>119880274</v>
       </c>
       <c r="B2" t="n">
-        <v>91463</v>
+        <v>87406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4745</v>
+        <v>4412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668983</v>
+        <v>668987</v>
       </c>
       <c r="R2" t="n">
-        <v>7181916</v>
+        <v>7181886</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880274</v>
+        <v>119880279</v>
       </c>
       <c r="B3" t="n">
-        <v>87406</v>
+        <v>57463</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4412</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668987</v>
+        <v>669087</v>
       </c>
       <c r="R3" t="n">
-        <v>7181886</v>
+        <v>7181763</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880276</v>
+        <v>119880273</v>
       </c>
       <c r="B4" t="n">
-        <v>78171</v>
+        <v>91463</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>4745</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668982</v>
+        <v>668983</v>
       </c>
       <c r="R4" t="n">
-        <v>7181867</v>
+        <v>7181916</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880279</v>
+        <v>119880276</v>
       </c>
       <c r="B5" t="n">
-        <v>57463</v>
+        <v>78171</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669087</v>
+        <v>668982</v>
       </c>
       <c r="R5" t="n">
-        <v>7181763</v>
+        <v>7181867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35790-2024 artfynd.xlsx
+++ b/artfynd/A 35790-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119880274</v>
+        <v>119880276</v>
       </c>
       <c r="B2" t="n">
-        <v>87406</v>
+        <v>78171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4412</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668987</v>
+        <v>668982</v>
       </c>
       <c r="R2" t="n">
-        <v>7181886</v>
+        <v>7181867</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880279</v>
+        <v>119880273</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
+        <v>91463</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4745</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669087</v>
+        <v>668983</v>
       </c>
       <c r="R3" t="n">
-        <v>7181763</v>
+        <v>7181916</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880273</v>
+        <v>119880274</v>
       </c>
       <c r="B4" t="n">
-        <v>91463</v>
+        <v>87406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4745</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668983</v>
+        <v>668987</v>
       </c>
       <c r="R4" t="n">
-        <v>7181916</v>
+        <v>7181886</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880276</v>
+        <v>119880279</v>
       </c>
       <c r="B5" t="n">
-        <v>78171</v>
+        <v>57463</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668982</v>
+        <v>669087</v>
       </c>
       <c r="R5" t="n">
-        <v>7181867</v>
+        <v>7181763</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35790-2024 artfynd.xlsx
+++ b/artfynd/A 35790-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119880276</v>
+        <v>119880273</v>
       </c>
       <c r="B2" t="n">
-        <v>78171</v>
+        <v>91481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>4745</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668982</v>
+        <v>668983</v>
       </c>
       <c r="R2" t="n">
-        <v>7181867</v>
+        <v>7181916</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880273</v>
+        <v>119880279</v>
       </c>
       <c r="B3" t="n">
-        <v>91463</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4745</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668983</v>
+        <v>669087</v>
       </c>
       <c r="R3" t="n">
-        <v>7181916</v>
+        <v>7181763</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>119880274</v>
       </c>
       <c r="B4" t="n">
-        <v>87406</v>
+        <v>87423</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880279</v>
+        <v>119880276</v>
       </c>
       <c r="B5" t="n">
-        <v>57463</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669087</v>
+        <v>668982</v>
       </c>
       <c r="R5" t="n">
-        <v>7181763</v>
+        <v>7181867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35790-2024 artfynd.xlsx
+++ b/artfynd/A 35790-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880279</v>
+        <v>119880276</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669087</v>
+        <v>668982</v>
       </c>
       <c r="R3" t="n">
-        <v>7181763</v>
+        <v>7181867</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880276</v>
+        <v>119880279</v>
       </c>
       <c r="B5" t="n">
-        <v>78187</v>
+        <v>57473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668982</v>
+        <v>669087</v>
       </c>
       <c r="R5" t="n">
-        <v>7181867</v>
+        <v>7181763</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35790-2024 artfynd.xlsx
+++ b/artfynd/A 35790-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880276</v>
+        <v>119880274</v>
       </c>
       <c r="B3" t="n">
-        <v>78187</v>
+        <v>87423</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>4412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668982</v>
+        <v>668987</v>
       </c>
       <c r="R3" t="n">
-        <v>7181867</v>
+        <v>7181886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880274</v>
+        <v>119880276</v>
       </c>
       <c r="B4" t="n">
-        <v>87423</v>
+        <v>78187</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4412</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668987</v>
+        <v>668982</v>
       </c>
       <c r="R4" t="n">
-        <v>7181886</v>
+        <v>7181867</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 35790-2024 artfynd.xlsx
+++ b/artfynd/A 35790-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119880273</v>
+        <v>119880279</v>
       </c>
       <c r="B2" t="n">
-        <v>91481</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4745</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668983</v>
+        <v>669087</v>
       </c>
       <c r="R2" t="n">
-        <v>7181916</v>
+        <v>7181763</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880276</v>
+        <v>119880273</v>
       </c>
       <c r="B4" t="n">
-        <v>78187</v>
+        <v>91481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>4745</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668982</v>
+        <v>668983</v>
       </c>
       <c r="R4" t="n">
-        <v>7181867</v>
+        <v>7181916</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880279</v>
+        <v>119880276</v>
       </c>
       <c r="B5" t="n">
-        <v>57473</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669087</v>
+        <v>668982</v>
       </c>
       <c r="R5" t="n">
-        <v>7181763</v>
+        <v>7181867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35790-2024 artfynd.xlsx
+++ b/artfynd/A 35790-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880274</v>
+        <v>119880276</v>
       </c>
       <c r="B3" t="n">
-        <v>87423</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4412</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668987</v>
+        <v>668982</v>
       </c>
       <c r="R3" t="n">
-        <v>7181886</v>
+        <v>7181867</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880273</v>
+        <v>119880274</v>
       </c>
       <c r="B4" t="n">
-        <v>91481</v>
+        <v>87423</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4745</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668983</v>
+        <v>668987</v>
       </c>
       <c r="R4" t="n">
-        <v>7181916</v>
+        <v>7181886</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880276</v>
+        <v>119880273</v>
       </c>
       <c r="B5" t="n">
-        <v>78187</v>
+        <v>91481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4745</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668982</v>
+        <v>668983</v>
       </c>
       <c r="R5" t="n">
-        <v>7181867</v>
+        <v>7181916</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
